--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:18:10+00:00</t>
+    <t>2023-04-28T11:24:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:11+00:00</t>
+    <t>2023-04-28T11:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:24:31+00:00</t>
+    <t>2023-04-30T03:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:40+00:00</t>
+    <t>2023-04-30T03:44:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:44:58+00:00</t>
+    <t>2023-04-30T03:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:52:18+00:00</t>
+    <t>2023-04-30T03:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T03:53:51+00:00</t>
+    <t>2023-04-30T09:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T09:28:44+00:00</t>
+    <t>2023-05-01T08:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:52:03+00:00</t>
+    <t>2023-05-01T08:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T08:56:42+00:00</t>
+    <t>2023-05-01T09:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:10:15+00:00</t>
+    <t>2023-05-01T09:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:11:26+00:00</t>
+    <t>2023-05-01T09:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:13:53+00:00</t>
+    <t>2023-05-01T09:16:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T09:16:45+00:00</t>
+    <t>2023-05-01T16:40:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:06+00:00</t>
+    <t>2023-05-01T16:40:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T16:40:27+00:00</t>
+    <t>2023-05-01T18:12:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:00+00:00</t>
+    <t>2023-05-01T18:12:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:12:07+00:00</t>
+    <t>2023-05-02T21:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:23:22+00:00</t>
+    <t>2023-05-02T21:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T21:27:47+00:00</t>
+    <t>2023-05-03T08:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:42:53+00:00</t>
+    <t>2023-05-05T21:01:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1397,44 +1397,45 @@
 </t>
   </si>
   <si>
+    <t>dateTime
+PeriodTiming</t>
+  </si>
+  <si>
+    <t>When service should occur</t>
+  </si>
+  <si>
+    <t>The date/time at which the requested service should occur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>TQ1/TQ2, OBR-7/OBR-8</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.planned</t>
+  </si>
+  <si>
+    <t>Procedure.procedureSchedule</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x]:occurrenceDateTime</t>
+  </si>
+  <si>
+    <t>occurrenceDateTime</t>
+  </si>
+  <si>
     <t xml:space="preserve">dateTime
 </t>
   </si>
   <si>
-    <t>When service should occur</t>
-  </si>
-  <si>
-    <t>The date/time at which the requested service should occur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Request.occurrence[x]</t>
-  </si>
-  <si>
-    <t>TQ1/TQ2, OBR-7/OBR-8</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.planned</t>
-  </si>
-  <si>
-    <t>Procedure.procedureSchedule</t>
-  </si>
-  <si>
-    <t>ServiceRequest.occurrence[x]:occurrenceDateTime</t>
-  </si>
-  <si>
-    <t>occurrenceDateTime</t>
-  </si>
-  <si>
     <t>ServiceRequest.asNeeded[x]</t>
   </si>
   <si>
@@ -1629,7 +1630,7 @@
     <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-for-assessment-or-test-not-performed</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-for-assessment</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1656,7 +1657,7 @@
     <t>ServiceRequest.reasonCode.text</t>
   </si>
   <si>
-    <t>Reason</t>
+    <t>Reason for testing</t>
   </si>
   <si>
     <t>ServiceRequest.reasonReference</t>
@@ -2185,7 +2186,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="126.34765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="85.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3510,13 +3511,13 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>81</v>
@@ -5507,13 +5508,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>81</v>
@@ -8079,7 +8080,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>89</v>
@@ -8146,7 +8147,7 @@
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>451</v>
+        <v>173</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>445</v>
@@ -8164,43 +8165,43 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>456</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>445</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>446</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>81</v>
@@ -8209,7 +8210,7 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>448</v>
@@ -8281,19 +8282,19 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>456</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -8439,7 +8440,7 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>469</v>
@@ -8776,7 +8777,7 @@
         <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2700" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2698" uniqueCount="589">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -284,6 +284,9 @@
     <t>Act[moodCode&lt;=INT]</t>
   </si>
   <si>
+    <t>clinical.general</t>
+  </si>
+  <si>
     <t>ServiceRequest.id</t>
   </si>
   <si>
@@ -367,7 +370,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -425,6 +428,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -465,7 +472,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -524,205 +531,199 @@
     <t>ServiceRequest.identifier.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.use</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.system</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.version</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.version</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.use</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.system</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.version</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.version</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -898,7 +899,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -979,7 +980,7 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this ServiceRequest.</t>
   </si>
   <si>
-    <t>Note: This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>Note: This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
   </si>
   <si>
     <t>Request.instantiatesCanonical</t>
@@ -1095,13 +1096,13 @@
     <t>The status of the order.</t>
   </si>
   <si>
-    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4/task.html) resource.</t>
+    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4B/task.html) resource.</t>
   </si>
   <si>
     <t>The status of a service order.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-status|4.3.0</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -1137,7 +1138,7 @@
     <t>The kind of service request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-intent|4.3.0</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -1194,7 +1195,7 @@
     <t>Identifies the level of importance to be assigned to actioning the request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
   </si>
   <si>
     <t>Request.priority</t>
@@ -1543,7 +1544,7 @@
     <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/participant-role</t>
+    <t>http://terminology.hl7.org/ValueSet/action-participant-role</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1575,7 +1576,7 @@
     <t>The desired performer for doing the requested service.  For example, the surgeon, dermatopathologist, endoscopist, etc.</t>
   </si>
   <si>
-    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
+    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4B/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
   </si>
   <si>
     <t>Request.performer</t>
@@ -1749,7 +1750,7 @@
     <t>One or more specimens that the laboratory procedure will use.</t>
   </si>
   <si>
-    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](http://hl7.org/fhir/R4/specimen.html) resource points to the ServiceRequest.</t>
+    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](http://hl7.org/fhir/R4B/specimen.html) resource points to the ServiceRequest.</t>
   </si>
   <si>
     <t>SPM</t>
@@ -1771,13 +1772,13 @@
     <t>Anatomic location where the procedure should be performed. This is the target site.</t>
   </si>
   <si>
-    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [procedure-targetBodyStructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
+    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [procedure-targetBodyStructure](http://hl7.org/fhir/R4B/extension-procedure-targetbodystructure.html).</t>
   </si>
   <si>
     <t>Knowing where the procedure is performed is important for tracking if multiple sites are possible.</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -2437,7 +2438,7 @@
         <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>81</v>
@@ -2445,10 +2446,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2459,7 +2460,7 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>81</v>
@@ -2468,19 +2469,19 @@
         <v>81</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2530,13 +2531,13 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>81</v>
@@ -2562,10 +2563,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2576,7 +2577,7 @@
         <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>81</v>
@@ -2585,16 +2586,16 @@
         <v>81</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2645,19 +2646,19 @@
         <v>81</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>81</v>
@@ -2677,10 +2678,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2691,28 +2692,28 @@
         <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2762,19 +2763,19 @@
         <v>81</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>81</v>
@@ -2794,10 +2795,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2808,7 +2809,7 @@
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>81</v>
@@ -2820,16 +2821,16 @@
         <v>81</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2855,13 +2856,13 @@
         <v>81</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>81</v>
@@ -2879,19 +2880,19 @@
         <v>81</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>81</v>
@@ -2911,21 +2912,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>81</v>
@@ -2937,16 +2938,16 @@
         <v>81</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2996,19 +2997,19 @@
         <v>81</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>81</v>
@@ -3017,7 +3018,7 @@
         <v>81</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>81</v>
@@ -3028,14 +3029,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -3054,16 +3055,16 @@
         <v>81</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3113,7 +3114,7 @@
         <v>81</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -3125,7 +3126,7 @@
         <v>81</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>81</v>
@@ -3134,7 +3135,7 @@
         <v>81</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>81</v>
@@ -3145,14 +3146,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3171,16 +3172,16 @@
         <v>81</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3230,7 +3231,7 @@
         <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -3242,7 +3243,7 @@
         <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>81</v>
@@ -3251,7 +3252,7 @@
         <v>81</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>81</v>
@@ -3262,14 +3263,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3282,25 +3283,25 @@
         <v>81</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -3349,7 +3350,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3361,7 +3362,7 @@
         <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -3370,7 +3371,7 @@
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>81</v>
@@ -3381,10 +3382,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3392,7 +3393,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>80</v>
@@ -3404,19 +3405,19 @@
         <v>81</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3454,19 +3455,19 @@
         <v>81</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3478,33 +3479,33 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>81</v>
@@ -3514,28 +3515,28 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3585,7 +3586,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3597,30 +3598,30 @@
         <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3631,7 +3632,7 @@
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
@@ -3643,13 +3644,13 @@
         <v>81</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3700,13 +3701,13 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>81</v>
@@ -3721,7 +3722,7 @@
         <v>81</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>81</v>
@@ -3732,14 +3733,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3758,16 +3759,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3805,19 +3806,19 @@
         <v>81</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3829,7 +3830,7 @@
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>81</v>
@@ -3838,7 +3839,7 @@
         <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>81</v>
@@ -3849,10 +3850,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3863,31 +3864,31 @@
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -3912,11 +3913,9 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y15" t="s" s="2">
         <v>182</v>
       </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>183</v>
       </c>
@@ -3942,19 +3941,19 @@
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>185</v>
@@ -3982,7 +3981,7 @@
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
@@ -3991,7 +3990,7 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>188</v>
@@ -4033,47 +4032,45 @@
       <c r="X16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>185</v>
@@ -4087,10 +4084,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4101,7 +4098,7 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -4113,13 +4110,13 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4170,13 +4167,13 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
@@ -4191,7 +4188,7 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -4202,14 +4199,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4228,16 +4225,16 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4275,19 +4272,19 @@
         <v>81</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4299,7 +4296,7 @@
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4308,7 +4305,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -4319,10 +4316,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4342,22 +4339,22 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4406,7 +4403,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4418,16 +4415,16 @@
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4438,10 +4435,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4452,7 +4449,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -4464,13 +4461,13 @@
         <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4521,13 +4518,13 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>81</v>
@@ -4542,7 +4539,7 @@
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -4553,14 +4550,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4579,16 +4576,16 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4626,19 +4623,19 @@
         <v>81</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4650,7 +4647,7 @@
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
@@ -4659,7 +4656,7 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4670,10 +4667,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4684,7 +4681,7 @@
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>81</v>
@@ -4693,22 +4690,22 @@
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4718,67 +4715,67 @@
         <v>81</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="T22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF22" t="s" s="2">
+      <c r="AG22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AG22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4789,10 +4786,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4803,7 +4800,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4812,10 +4809,10 @@
         <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>228</v>
@@ -4880,13 +4877,13 @@
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
@@ -4920,7 +4917,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>81</v>
@@ -4929,10 +4926,10 @@
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>236</v>
@@ -4952,7 +4949,7 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>81</v>
@@ -4997,13 +4994,13 @@
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
@@ -5037,7 +5034,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -5046,10 +5043,10 @@
         <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>244</v>
@@ -5114,13 +5111,13 @@
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>81</v>
@@ -5154,7 +5151,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -5163,7 +5160,7 @@
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>253</v>
@@ -5233,13 +5230,13 @@
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>81</v>
@@ -5273,7 +5270,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -5282,10 +5279,10 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>263</v>
@@ -5352,13 +5349,13 @@
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>81</v>
@@ -5389,10 +5386,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -5401,10 +5398,10 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>273</v>
@@ -5471,13 +5468,13 @@
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
@@ -5511,19 +5508,19 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>284</v>
@@ -5588,13 +5585,13 @@
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
@@ -5628,7 +5625,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5637,7 +5634,7 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>293</v>
@@ -5703,13 +5700,13 @@
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
@@ -5743,7 +5740,7 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
@@ -5752,7 +5749,7 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>301</v>
@@ -5820,13 +5817,13 @@
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
@@ -5869,7 +5866,7 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>309</v>
@@ -5943,7 +5940,7 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>313</v>
@@ -5986,10 +5983,10 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>317</v>
@@ -6060,7 +6057,7 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>320</v>
@@ -6103,7 +6100,7 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>323</v>
@@ -6175,7 +6172,7 @@
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>326</v>
@@ -6218,7 +6215,7 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>331</v>
@@ -6290,7 +6287,7 @@
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>334</v>
@@ -6324,7 +6321,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -6333,10 +6330,10 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>339</v>
@@ -6403,13 +6400,13 @@
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>343</v>
@@ -6440,22 +6437,22 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>347</v>
@@ -6490,7 +6487,7 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y37" t="s" s="2">
         <v>350</v>
@@ -6517,16 +6514,16 @@
         <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>352</v>
@@ -6557,22 +6554,22 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>358</v>
@@ -6607,7 +6604,7 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y38" t="s" s="2">
         <v>362</v>
@@ -6634,22 +6631,22 @@
         <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>364</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>365</v>
@@ -6686,7 +6683,7 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>188</v>
@@ -6762,7 +6759,7 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6796,7 +6793,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6805,10 +6802,10 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>378</v>
@@ -6843,7 +6840,7 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y40" t="s" s="2">
         <v>381</v>
@@ -6873,13 +6870,13 @@
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>383</v>
@@ -6913,16 +6910,16 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>253</v>
@@ -6994,13 +6991,13 @@
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>393</v>
@@ -7031,10 +7028,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -7043,7 +7040,7 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>188</v>
@@ -7081,7 +7078,7 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
@@ -7109,13 +7106,13 @@
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>401</v>
@@ -7149,7 +7146,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7161,13 +7158,13 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7218,13 +7215,13 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
@@ -7239,7 +7236,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7257,7 +7254,7 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7276,16 +7273,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7323,19 +7320,19 @@
         <v>81</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7347,7 +7344,7 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7356,7 +7353,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7390,22 +7387,22 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7454,7 +7451,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7466,16 +7463,16 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7500,7 +7497,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7509,10 +7506,10 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>263</v>
@@ -7579,13 +7576,13 @@
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
@@ -7628,7 +7625,7 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>188</v>
@@ -7702,7 +7699,7 @@
         <v>418</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7736,7 +7733,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7745,7 +7742,7 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>421</v>
@@ -7813,13 +7810,13 @@
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7850,10 +7847,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7862,7 +7859,7 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>427</v>
@@ -7925,16 +7922,16 @@
         <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>430</v>
@@ -7965,10 +7962,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7977,7 +7974,7 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>437</v>
@@ -8043,13 +8040,13 @@
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>440</v>
@@ -8083,7 +8080,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -8092,7 +8089,7 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>447</v>
@@ -8147,7 +8144,7 @@
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>445</v>
@@ -8156,13 +8153,13 @@
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>451</v>
@@ -8198,16 +8195,16 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>458</v>
@@ -8273,13 +8270,13 @@
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>451</v>
@@ -8313,7 +8310,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -8322,7 +8319,7 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>460</v>
@@ -8388,13 +8385,13 @@
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -8428,7 +8425,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8437,7 +8434,7 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>458</v>
@@ -8503,13 +8500,13 @@
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>471</v>
@@ -8540,10 +8537,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8552,7 +8549,7 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>478</v>
@@ -8620,13 +8617,13 @@
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>482</v>
@@ -8660,7 +8657,7 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8669,7 +8666,7 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>188</v>
@@ -8737,13 +8734,13 @@
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>494</v>
@@ -8774,10 +8771,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8786,7 +8783,7 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>500</v>
@@ -8860,7 +8857,7 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>504</v>
@@ -8903,7 +8900,7 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>188</v>
@@ -8975,7 +8972,7 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
@@ -9018,7 +9015,7 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>514</v>
@@ -9090,7 +9087,7 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9121,7 +9118,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>80</v>
@@ -9133,7 +9130,7 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>188</v>
@@ -9171,7 +9168,7 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
@@ -9205,7 +9202,7 @@
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>522</v>
@@ -9239,7 +9236,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -9251,13 +9248,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9308,13 +9305,13 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
@@ -9329,7 +9326,7 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -9347,7 +9344,7 @@
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9366,16 +9363,16 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9413,19 +9410,19 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9437,7 +9434,7 @@
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -9446,7 +9443,7 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -9480,22 +9477,22 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9544,7 +9541,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9556,16 +9553,16 @@
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9590,7 +9587,7 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -9599,10 +9596,10 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>263</v>
@@ -9669,13 +9666,13 @@
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -9718,7 +9715,7 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>532</v>
@@ -9792,7 +9789,7 @@
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>536</v>
@@ -9907,7 +9904,7 @@
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>543</v>
@@ -10024,7 +10021,7 @@
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>552</v>
@@ -10055,10 +10052,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -10067,7 +10064,7 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>556</v>
@@ -10141,7 +10138,7 @@
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
@@ -10184,7 +10181,7 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>188</v>
@@ -10260,7 +10257,7 @@
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>81</v>
@@ -10297,7 +10294,7 @@
         <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>81</v>
@@ -10375,7 +10372,7 @@
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>575</v>
@@ -10409,7 +10406,7 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>81</v>
@@ -10418,10 +10415,10 @@
         <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>579</v>
@@ -10484,13 +10481,13 @@
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -10607,13 +10604,13 @@
         <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>587</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>588</v>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2698" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2700" uniqueCount="589">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -284,9 +284,6 @@
     <t>Act[moodCode&lt;=INT]</t>
   </si>
   <si>
-    <t>clinical.general</t>
-  </si>
-  <si>
     <t>ServiceRequest.id</t>
   </si>
   <si>
@@ -370,7 +367,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -428,10 +425,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -472,7 +465,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -531,6 +524,10 @@
     <t>ServiceRequest.identifier.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -586,7 +583,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -620,6 +620,9 @@
     <t>extensible</t>
   </si>
   <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
@@ -720,10 +723,6 @@
     <t>ServiceRequest.identifier.type.coding.version</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -899,7 +898,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -980,7 +979,7 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this ServiceRequest.</t>
   </si>
   <si>
-    <t>Note: This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>Note: This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
   </si>
   <si>
     <t>Request.instantiatesCanonical</t>
@@ -1096,13 +1095,13 @@
     <t>The status of the order.</t>
   </si>
   <si>
-    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4B/task.html) resource.</t>
+    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4/task.html) resource.</t>
   </si>
   <si>
     <t>The status of a service order.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -1138,7 +1137,7 @@
     <t>The kind of service request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-intent|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -1195,7 +1194,7 @@
     <t>Identifies the level of importance to be assigned to actioning the request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
   </si>
   <si>
     <t>Request.priority</t>
@@ -1544,7 +1543,7 @@
     <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/action-participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/participant-role</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1576,7 +1575,7 @@
     <t>The desired performer for doing the requested service.  For example, the surgeon, dermatopathologist, endoscopist, etc.</t>
   </si>
   <si>
-    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4B/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
+    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
   </si>
   <si>
     <t>Request.performer</t>
@@ -1750,7 +1749,7 @@
     <t>One or more specimens that the laboratory procedure will use.</t>
   </si>
   <si>
-    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](http://hl7.org/fhir/R4B/specimen.html) resource points to the ServiceRequest.</t>
+    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](http://hl7.org/fhir/R4/specimen.html) resource points to the ServiceRequest.</t>
   </si>
   <si>
     <t>SPM</t>
@@ -1772,13 +1771,13 @@
     <t>Anatomic location where the procedure should be performed. This is the target site.</t>
   </si>
   <si>
-    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [procedure-targetBodyStructure](http://hl7.org/fhir/R4B/extension-procedure-targetbodystructure.html).</t>
+    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [procedure-targetBodyStructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
   </si>
   <si>
     <t>Knowing where the procedure is performed is important for tracking if multiple sites are possible.</t>
   </si>
   <si>
-    <t>SNOMED CT Body site concepts</t>
+    <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -2438,7 +2437,7 @@
         <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>81</v>
@@ -2446,10 +2445,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2460,28 +2459,28 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2531,13 +2530,13 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>81</v>
@@ -2563,10 +2562,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2577,25 +2576,25 @@
         <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2646,19 +2645,19 @@
         <v>81</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>81</v>
@@ -2678,10 +2677,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2692,28 +2691,28 @@
         <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2763,19 +2762,19 @@
         <v>81</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>81</v>
@@ -2795,10 +2794,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2809,7 +2808,7 @@
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>81</v>
@@ -2821,16 +2820,16 @@
         <v>81</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2856,43 +2855,43 @@
         <v>81</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>117</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>81</v>
@@ -2912,21 +2911,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>81</v>
@@ -2938,16 +2937,16 @@
         <v>81</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2997,28 +2996,28 @@
         <v>81</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM7" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>81</v>
@@ -3029,14 +3028,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -3055,16 +3054,16 @@
         <v>81</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3114,7 +3113,7 @@
         <v>81</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -3126,7 +3125,7 @@
         <v>81</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>81</v>
@@ -3135,7 +3134,7 @@
         <v>81</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>81</v>
@@ -3146,14 +3145,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3172,16 +3171,16 @@
         <v>81</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3231,7 +3230,7 @@
         <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -3243,7 +3242,7 @@
         <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>81</v>
@@ -3252,7 +3251,7 @@
         <v>81</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>81</v>
@@ -3263,14 +3262,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3283,25 +3282,25 @@
         <v>81</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -3350,7 +3349,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3362,7 +3361,7 @@
         <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -3371,7 +3370,7 @@
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>81</v>
@@ -3382,10 +3381,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3393,7 +3392,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>80</v>
@@ -3405,19 +3404,19 @@
         <v>81</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3455,19 +3454,19 @@
         <v>81</v>
       </c>
       <c r="AB11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AC11" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>155</v>
-      </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3479,33 +3478,33 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>160</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>81</v>
@@ -3515,28 +3514,28 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H12" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H12" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="I12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3586,7 +3585,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3598,30 +3597,30 @@
         <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>160</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3632,7 +3631,7 @@
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
@@ -3644,13 +3643,13 @@
         <v>81</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3701,28 +3700,28 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>81</v>
@@ -3733,14 +3732,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3759,16 +3758,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3806,19 +3805,19 @@
         <v>81</v>
       </c>
       <c r="AB14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AC14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AC14" t="s" s="2">
+      <c r="AD14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AD14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE14" t="s" s="2">
+      <c r="AF14" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3830,7 +3829,7 @@
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>81</v>
@@ -3839,7 +3838,7 @@
         <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>81</v>
@@ -3850,10 +3849,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3864,31 +3863,31 @@
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -3913,9 +3912,11 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>183</v>
       </c>
@@ -3941,19 +3942,19 @@
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>185</v>
@@ -3981,16 +3982,16 @@
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>188</v>
@@ -4032,9 +4033,11 @@
       <c r="X16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y16" s="2"/>
+      <c r="Y16" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -4052,25 +4055,25 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>185</v>
@@ -4084,10 +4087,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4098,7 +4101,7 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -4110,13 +4113,13 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4167,28 +4170,28 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -4199,14 +4202,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4225,16 +4228,16 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4272,19 +4275,19 @@
         <v>81</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4296,7 +4299,7 @@
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4305,7 +4308,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -4316,10 +4319,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4339,22 +4342,22 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4403,7 +4406,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4415,16 +4418,16 @@
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4435,10 +4438,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4449,7 +4452,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -4461,13 +4464,13 @@
         <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4518,28 +4521,28 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -4550,14 +4553,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4576,16 +4579,16 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4623,19 +4626,19 @@
         <v>81</v>
       </c>
       <c r="AB21" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AC21" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AC21" t="s" s="2">
+      <c r="AD21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE21" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AD21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE21" t="s" s="2">
+      <c r="AF21" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4647,7 +4650,7 @@
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
@@ -4656,7 +4659,7 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4667,10 +4670,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4681,31 +4684,31 @@
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4715,7 +4718,7 @@
         <v>81</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>81</v>
@@ -4754,28 +4757,28 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4786,10 +4789,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4800,19 +4803,19 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K23" t="s" s="2">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>228</v>
@@ -4877,13 +4880,13 @@
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
@@ -4917,19 +4920,19 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>236</v>
@@ -4949,7 +4952,7 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>81</v>
@@ -4994,13 +4997,13 @@
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
@@ -5034,19 +5037,19 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>244</v>
@@ -5111,13 +5114,13 @@
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>81</v>
@@ -5151,16 +5154,16 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>253</v>
@@ -5230,13 +5233,13 @@
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>81</v>
@@ -5270,19 +5273,19 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>263</v>
@@ -5349,13 +5352,13 @@
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>81</v>
@@ -5386,22 +5389,22 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>273</v>
@@ -5468,13 +5471,13 @@
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
@@ -5508,19 +5511,19 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H29" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H29" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="I29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>284</v>
@@ -5585,13 +5588,13 @@
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
@@ -5625,16 +5628,16 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>293</v>
@@ -5700,13 +5703,13 @@
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
@@ -5740,16 +5743,16 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>301</v>
@@ -5817,13 +5820,13 @@
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
@@ -5866,7 +5869,7 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>309</v>
@@ -5940,7 +5943,7 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>313</v>
@@ -5983,10 +5986,10 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>317</v>
@@ -6057,7 +6060,7 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>320</v>
@@ -6100,7 +6103,7 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>323</v>
@@ -6172,7 +6175,7 @@
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>326</v>
@@ -6215,7 +6218,7 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>331</v>
@@ -6287,7 +6290,7 @@
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>334</v>
@@ -6321,19 +6324,19 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>339</v>
@@ -6400,13 +6403,13 @@
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>343</v>
@@ -6437,22 +6440,22 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I37" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G37" t="s" s="2">
+      <c r="J37" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K37" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>347</v>
@@ -6487,7 +6490,7 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y37" t="s" s="2">
         <v>350</v>
@@ -6514,16 +6517,16 @@
         <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>352</v>
@@ -6554,22 +6557,22 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I38" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G38" t="s" s="2">
+      <c r="J38" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>358</v>
@@ -6604,7 +6607,7 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y38" t="s" s="2">
         <v>362</v>
@@ -6631,22 +6634,22 @@
         <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>364</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>365</v>
@@ -6683,7 +6686,7 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>188</v>
@@ -6759,7 +6762,7 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6793,19 +6796,19 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K40" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>378</v>
@@ -6840,7 +6843,7 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y40" t="s" s="2">
         <v>381</v>
@@ -6870,13 +6873,13 @@
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>383</v>
@@ -6910,16 +6913,16 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I41" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>253</v>
@@ -6991,13 +6994,13 @@
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>393</v>
@@ -7028,19 +7031,19 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J42" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>188</v>
@@ -7078,7 +7081,7 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
@@ -7106,13 +7109,13 @@
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>401</v>
@@ -7146,7 +7149,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7158,13 +7161,13 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7215,28 +7218,28 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7254,7 +7257,7 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7273,16 +7276,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7320,19 +7323,19 @@
         <v>81</v>
       </c>
       <c r="AB44" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AC44" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AC44" t="s" s="2">
+      <c r="AD44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE44" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AD44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE44" t="s" s="2">
+      <c r="AF44" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7344,7 +7347,7 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7353,7 +7356,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7387,22 +7390,22 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7451,7 +7454,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7463,16 +7466,16 @@
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7497,19 +7500,19 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J46" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K46" t="s" s="2">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>263</v>
@@ -7576,13 +7579,13 @@
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
@@ -7625,7 +7628,7 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>188</v>
@@ -7699,7 +7702,7 @@
         <v>418</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7733,16 +7736,16 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>421</v>
@@ -7810,13 +7813,13 @@
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7847,19 +7850,19 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>427</v>
@@ -7922,16 +7925,16 @@
         <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>430</v>
@@ -7962,19 +7965,19 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J50" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>437</v>
@@ -8040,13 +8043,13 @@
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>440</v>
@@ -8080,16 +8083,16 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J51" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>447</v>
@@ -8144,7 +8147,7 @@
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>445</v>
@@ -8153,13 +8156,13 @@
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>451</v>
@@ -8195,16 +8198,16 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H52" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H52" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="I52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>458</v>
@@ -8270,13 +8273,13 @@
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>451</v>
@@ -8310,16 +8313,16 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>460</v>
@@ -8385,13 +8388,13 @@
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -8425,16 +8428,16 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J54" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>458</v>
@@ -8500,13 +8503,13 @@
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>471</v>
@@ -8537,19 +8540,19 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J55" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>478</v>
@@ -8617,13 +8620,13 @@
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>482</v>
@@ -8657,16 +8660,16 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>188</v>
@@ -8734,13 +8737,13 @@
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>494</v>
@@ -8771,19 +8774,19 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J57" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>500</v>
@@ -8857,7 +8860,7 @@
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>504</v>
@@ -8900,7 +8903,7 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>188</v>
@@ -8972,7 +8975,7 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
@@ -9015,7 +9018,7 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>514</v>
@@ -9087,7 +9090,7 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9118,7 +9121,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>80</v>
@@ -9130,7 +9133,7 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>188</v>
@@ -9168,7 +9171,7 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
@@ -9202,7 +9205,7 @@
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>522</v>
@@ -9236,7 +9239,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -9248,13 +9251,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9305,28 +9308,28 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -9344,7 +9347,7 @@
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9363,16 +9366,16 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9410,19 +9413,19 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AC62" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AC62" t="s" s="2">
+      <c r="AD62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE62" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="AD62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE62" t="s" s="2">
+      <c r="AF62" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9434,7 +9437,7 @@
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -9443,7 +9446,7 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -9477,22 +9480,22 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9541,7 +9544,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9553,16 +9556,16 @@
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9587,19 +9590,19 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J64" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K64" t="s" s="2">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>263</v>
@@ -9666,13 +9669,13 @@
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
@@ -9715,7 +9718,7 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>532</v>
@@ -9789,7 +9792,7 @@
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>536</v>
@@ -9904,7 +9907,7 @@
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>543</v>
@@ -10021,7 +10024,7 @@
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>552</v>
@@ -10052,19 +10055,19 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J68" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>556</v>
@@ -10138,7 +10141,7 @@
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
@@ -10181,7 +10184,7 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>188</v>
@@ -10257,7 +10260,7 @@
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>81</v>
@@ -10294,7 +10297,7 @@
         <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>81</v>
@@ -10372,7 +10375,7 @@
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>575</v>
@@ -10406,19 +10409,19 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J71" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="H71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>91</v>
-      </c>
       <c r="K71" t="s" s="2">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>579</v>
@@ -10481,13 +10484,13 @@
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -10604,13 +10607,13 @@
         <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>587</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>588</v>

--- a/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/Richard/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
